--- a/MATH/M05/bus123-math-m05-l01-starter.xlsx
+++ b/MATH/M05/bus123-math-m05-l01-starter.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
@@ -13,7 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -24,67 +19,82 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <i val="1"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB8843D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF355773"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -93,121 +103,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E1116"/>
+        <fgColor rgb="FF0E1116"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="FFFAF8F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C5E"/>
+        <fgColor rgb="FF4A7C5E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2EEE5"/>
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EC"/>
+        <fgColor rgb="FFEAF3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
+        <fgColor rgb="FFFFF3C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
+        <fgColor rgb="FFE8F0FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00355773"/>
+        <fgColor rgb="FF355773"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FFE5E1D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </left>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E5E1D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E1D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E5E1D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E1D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E1D6"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -290,11 +336,57 @@
     <xf numFmtId="166" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -367,7 +459,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -409,72 +501,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -530,7 +564,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -539,13 +573,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -579,17 +613,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -644,8 +667,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -850,7 +871,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1151,7 +1172,7 @@
           <t>Self-check score</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="51">
         <f>COUNTIF(F5:F15,"Correct*")&amp;" of 9 complete"</f>
         <v/>
       </c>
@@ -1166,7 +1187,7 @@
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1769,7 +1790,7 @@
           <t>Submission reminder</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="52" t="inlineStr">
         <is>
           <t>Complete every blue formula cell and write a short interpretation. Live You Try It is practice; Class Challenge is the graded or next-level activity.</t>
         </is>
@@ -1788,7 +1809,7 @@
     <mergeCell ref="C21:J21"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1801,229 +1822,172 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="21.11000061035156" customWidth="1" min="1" max="1"/>
+    <col width="25.55999946594238" customWidth="1" min="2" max="2"/>
+    <col width="34.43999862670898" customWidth="1" min="3" max="3"/>
+    <col width="33.33000183105469" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Formula Reference Card - MATH M05 L01</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Payroll and depreciation syntax reminders. Use cell references whenever possible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>Excel Pattern</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>Plain-English Meaning</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+    <row r="2" ht="31.5" customHeight="1">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Weekly salary pay</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =AnnualSalary/52</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>=AnnualSalary/52</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="inlineStr">
         <is>
           <t>Converts annual salary into weekly pay.</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Pay frequency changes the check size, not total salary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="D2" s="50" t="inlineStr">
+        <is>
+          <t>Pay frequency changes check size, not total salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>Regular pay</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =MIN(Hours,40)*Rate</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>=MIN(Hours,40)*Rate</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="inlineStr">
         <is>
           <t>Caps regular hours at 40.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Do not pay all 43 hours at regular rate when OT exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
+        <is>
+          <t>Do not pay all hours at regular rate when OT exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Overtime pay</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =MAX(Hours-40,0)*Rate*1.5</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
+        <is>
+          <t>=MAX(Hours-40,0)*Rate*1.5</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Pays only hours above threshold at premium rate.</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>MAX prevents negative overtime.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Gross pay</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =RegularPay+OvertimePay</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>=RegularPay+OvertimePay</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>Total before deductions.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>Gross pay is not take-home pay.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Team payroll</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =Employees*GrossPayPerEmployee</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Scales one-person pay to a team.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>A small weekly difference compounds annually.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Annual depreciation</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =(Cost-ResidualValue)/UsefulLife</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>=(Cost-ResidualValue)/UsefulLife</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>Spreads depreciable cost evenly.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>Subtract residual value before dividing.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Accumulated depreciation</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =AnnualDepreciation*YearsRecorded</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Running total of depreciation so far.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated is not the same as one-year expense.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+    <row r="7" ht="31.5" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Book value</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> =Cost-AccumulatedDepreciation</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>=Cost-AccumulatedDepreciation</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Remaining recorded value.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>Book value should fall to residual value, not zero.</t>
         </is>
       </c>
     </row>
+    <row r="8" ht="40" customHeight="1"/>
+    <row r="9" ht="40" customHeight="1"/>
+    <row r="10" ht="40" customHeight="1"/>
+    <row r="11" ht="40" customHeight="1"/>
+    <row r="12" ht="40" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MATH/M05/bus123-math-m05-l01-starter.xlsx
+++ b/MATH/M05/bus123-math-m05-l01-starter.xlsx
@@ -14,10 +14,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -253,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -382,6 +384,36 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -728,7 +760,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>During the deck, open Live You Try It for short Excel pauses after worked examples.</t>
+          <t>During the deck, open Live You Try It. Type the slide givens into the input cells first, then build formulas that reference those cells.</t>
         </is>
       </c>
     </row>
@@ -740,7 +772,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Live You Try It is self-graded. Hints and feedback help you fix formulas before moving on.</t>
+          <t>Live You Try It is self-graded. Hints and feedback help you revise before moving on; it is not part of the graded Class Challenge.</t>
         </is>
       </c>
     </row>
@@ -838,7 +870,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Student input cells.</t>
+          <t>Slide-given input cells on Live You Try It.</t>
         </is>
       </c>
     </row>
@@ -881,15 +913,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -900,13 +936,13 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Self-graded Excel pauses using the exact numbers from the slides. Use feedback to revise; this tab is not the graded contract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Self-graded Excel pauses: type the slide givens first, then build formulas that reference those input cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Slide</t>
@@ -914,278 +950,312 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Pause / task</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Given facts</t>
+          <t>Given 1</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Your formula / result</t>
+          <t>Given 2</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Given 3</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Given 4</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Given 5</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Formula answer</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>Hint</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Feedback</t>
         </is>
       </c>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Weekly salary check</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>$52,000 annual salary and 52 weekly pay periods</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Weekly salary check - Type annual salary and weekly pay periods, then calculate weekly pay.</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="n"/>
+      <c r="D5" s="57" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="58" t="n"/>
+      <c r="I5" s="55" t="inlineStr">
         <is>
           <t>Divide annual salary by weekly pay periods.</t>
         </is>
       </c>
-      <c r="F5" s="12">
-        <f>IF(D5="","Hint: "&amp;E5,IF(ROUND(D5,2)=ROUND(1000,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J5" s="59">
+        <f>IF(COUNTBLANK(C5:D5)&gt;0,"Start here: Divide annual salary by weekly pay periods.",IF(H5="","Next: build a formula in H5 that references your given cells.",IF(AND(AND(ABS(C5-52000)&lt;0.01,ABS(D5-52)&lt;0.01),ABS(H5-(C5/D5))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K5" s="59" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>One nurse regular pay</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>40 regular hours at $44 per hour</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>One nurse regular pay - Type regular hours and hourly rate, then calculate regular pay.</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="n"/>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="58" t="n"/>
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>Regular pay uses the first 40 hours.</t>
         </is>
       </c>
-      <c r="F6" s="12">
-        <f>IF(D6="","Hint: "&amp;E6,IF(ROUND(D6,2)=ROUND(1760,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J6" s="59">
+        <f>IF(COUNTBLANK(C6:D6)&gt;0,"Start here: Regular pay uses the first 40 hours.",IF(H6="","Next: build a formula in H6 that references your given cells.",IF(AND(AND(ABS(C6-40)&lt;0.01,ABS(D6-44)&lt;0.01),ABS(H6-(C6*D6))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K6" s="59" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>One nurse gross pay</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>43 hours at $44 per hour with 1.5x overtime</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>One nurse gross pay - Type total hours, regular-hours cap, hourly rate, and OT multiplier.</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="n"/>
+      <c r="D7" s="57" t="n"/>
+      <c r="E7" s="58" t="n"/>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="58" t="n"/>
+      <c r="I7" s="55" t="inlineStr">
         <is>
           <t>Separate regular hours from overtime hours.</t>
         </is>
       </c>
-      <c r="F7" s="12">
-        <f>IF(D7="","Hint: "&amp;E7,IF(ROUND(D7,2)=ROUND(1958,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J7" s="59">
+        <f>IF(COUNTBLANK(C7:F7)&gt;0,"Start here: Separate regular hours from overtime hours.",IF(H7="","Next: build a formula in H7 that references your given cells.",IF(AND(AND(ABS(C7-43)&lt;0.01,ABS(D7-40)&lt;0.01,ABS(E7-44)&lt;0.01,ABS(F7-1.5)&lt;0.01),ABS(H7-(MIN(C7,D7)*E7+MAX(C7-D7,0)*E7*F7))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
-    </row>
-    <row r="8" ht="8" customHeight="1"/>
+      <c r="K7" s="59" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1"/>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Team regular pay</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>8 nurses, 40 regular hours each, $44 per hour</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Multiply the regular pay by the number of nurses.</t>
-        </is>
-      </c>
-      <c r="F9" s="12">
-        <f>IF(D9="","Hint: "&amp;E9,IF(ROUND(D9,2)=ROUND(14080,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>Team regular pay - Type nurses, regular hours, and rate, then calculate team regular pay.</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="58" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="58" t="n"/>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>Multiply one regular-pay setup by the number of nurses.</t>
+        </is>
+      </c>
+      <c r="J9" s="59">
+        <f>IF(COUNTBLANK(C9:E9)&gt;0,"Start here: Multiply one regular-pay setup by the number of nurses.",IF(H9="","Next: build a formula in H9 that references your given cells.",IF(AND(AND(ABS(C9-8)&lt;0.01,ABS(D9-40)&lt;0.01,ABS(E9-44)&lt;0.01),ABS(H9-(C9*D9*E9))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K9" s="59" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Team overtime pay</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>8 nurses, 3 overtime hours each, $44 per hour, 1.5x OT</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>Team overtime pay - Type nurses, overtime hours, rate, and OT multiplier.</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="n"/>
+      <c r="D10" s="57" t="n"/>
+      <c r="E10" s="58" t="n"/>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="58" t="n"/>
+      <c r="I10" s="55" t="inlineStr">
         <is>
           <t>Overtime uses only the 3 hours above 40.</t>
         </is>
       </c>
-      <c r="F10" s="12">
-        <f>IF(D10="","Hint: "&amp;E10,IF(ROUND(D10,2)=ROUND(1584,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J10" s="59">
+        <f>IF(COUNTBLANK(C10:F10)&gt;0,"Start here: Overtime uses only the 3 hours above 40.",IF(H10="","Next: build a formula in H10 that references your given cells.",IF(AND(AND(ABS(C10-8)&lt;0.01,ABS(D10-3)&lt;0.01,ABS(E10-44)&lt;0.01,ABS(F10-1.5)&lt;0.01),ABS(H10-(C10*D10*E10*F10))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K10" s="59" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Team gross pay</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Team regular pay plus team overtime pay</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Gross pay adds regular and overtime pay.</t>
-        </is>
-      </c>
-      <c r="F11" s="12">
-        <f>IF(D11="","Hint: "&amp;E11,IF(ROUND(D11,2)=ROUND(15664,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Team gross pay - Type nurses, regular hours, rate, OT hours, and OT multiplier.</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="60" t="n"/>
+      <c r="H11" s="58" t="n"/>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>Gross pay adds team regular pay and team overtime pay.</t>
+        </is>
+      </c>
+      <c r="J11" s="59">
+        <f>IF(COUNTBLANK(C11:G11)&gt;0,"Start here: Gross pay adds team regular pay and team overtime pay.",IF(H11="","Next: build a formula in H11 that references your given cells.",IF(AND(AND(ABS(C11-8)&lt;0.01,ABS(D11-40)&lt;0.01,ABS(E11-44)&lt;0.01,ABS(F11-3)&lt;0.01,ABS(G11-1.5)&lt;0.01),ABS(H11-(C11*D11*E11+C11*F11*E11*G11))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
+      <c r="K11" s="59" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1"/>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="54" t="n">
         <v>17</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Annual depreciation</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>$84,000 cost, $12,000 residual value, 6-year life</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>Annual depreciation - Type cost, residual value, and useful life, then calculate annual depreciation.</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="n"/>
+      <c r="D13" s="56" t="n"/>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="58" t="n"/>
+      <c r="I13" s="55" t="inlineStr">
         <is>
           <t>Subtract residual value before dividing by life.</t>
         </is>
       </c>
-      <c r="F13" s="12">
-        <f>IF(D13="","Hint: "&amp;E13,IF(ROUND(D13,2)=ROUND(12000,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J13" s="59">
+        <f>IF(COUNTBLANK(C13:E13)&gt;0,"Start here: Subtract residual value before dividing by life.",IF(H13="","Next: build a formula in H13 that references your given cells.",IF(AND(AND(ABS(C13-84000)&lt;0.01,ABS(D13-12000)&lt;0.01,ABS(E13-6)&lt;0.01),ABS(H13-((C13-D13)/E13))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K13" s="59" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Year 3 accumulated depreciation</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>$12,000 annual depreciation for 3 years</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>Year 3 accumulated depreciation - Type annual depreciation and years recorded, then calculate accumulated depreciation.</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="57" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="58" t="n"/>
+      <c r="I14" s="55" t="inlineStr">
         <is>
           <t>Accumulated depreciation is the running total.</t>
         </is>
       </c>
-      <c r="F14" s="12">
-        <f>IF(D14="","Hint: "&amp;E14,IF(ROUND(D14,2)=ROUND(36000,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J14" s="59">
+        <f>IF(COUNTBLANK(C14:D14)&gt;0,"Start here: Accumulated depreciation is the running total.",IF(H14="","Next: build a formula in H14 that references your given cells.",IF(AND(AND(ABS(C14-12000)&lt;0.01,ABS(D14-3)&lt;0.01),ABS(H14-(C14*D14))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
+      <c r="K14" s="59" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Year 3 book value</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>$84,000 cost less Year 3 accumulated depreciation</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Year 3 book value - Type original cost and Year 3 accumulated depreciation, then calculate book value.</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="n"/>
+      <c r="D15" s="56" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="55" t="inlineStr">
         <is>
           <t>Book value is cost minus accumulated depreciation.</t>
         </is>
       </c>
-      <c r="F15" s="12">
-        <f>IF(D15="","Hint: "&amp;E15,IF(ROUND(D15,2)=ROUND(48000,2),"Correct - self-check complete","Try again - revise the formula or input."))</f>
+      <c r="J15" s="59">
+        <f>IF(COUNTBLANK(C15:D15)&gt;0,"Start here: Book value is cost minus accumulated depreciation.",IF(H15="","Next: build a formula in H15 that references your given cells.",IF(AND(AND(ABS(C15-84000)&lt;0.01,ABS(D15-36000)&lt;0.01),ABS(H15-(C15-D15))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
-    </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17">
+      <c r="K15" s="59" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Self-check score</t>
         </is>
       </c>
-      <c r="B17" s="51">
-        <f>COUNTIF(F5:F15,"Correct*")&amp;" of 9 complete"</f>
+      <c r="B17" s="61">
+        <f>COUNTIF(J5:J15,"Correct*")&amp;" of 9 complete"</f>
         <v/>
       </c>
       <c r="C17" s="15" t="n"/>
       <c r="D17" s="15" t="n"/>
       <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1274,7 +1344,7 @@
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>Instructor review note</t>
+          <t>Review note</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1376,7 @@
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1408,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1440,7 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1476,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1512,7 @@
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1546,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1584,7 @@
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1622,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1654,7 @@
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1688,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1720,7 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1754,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1786,7 @@
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1818,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1850,7 @@
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>Formula required; interpretation reviewed separately.</t>
+          <t>Formula required; interpretation can be reviewed separately.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.11000061035156" customWidth="1" min="1" max="1"/>
@@ -1856,7 +1926,7 @@
           <t>Weekly salary pay</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>=AnnualSalary/52</t>
         </is>
@@ -1878,7 +1948,7 @@
           <t>Regular pay</t>
         </is>
       </c>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>=MIN(Hours,40)*Rate</t>
         </is>
@@ -1900,7 +1970,7 @@
           <t>Overtime pay</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>=MAX(Hours-40,0)*Rate*1.5</t>
         </is>
@@ -1922,7 +1992,7 @@
           <t>Gross pay</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>=RegularPay+OvertimePay</t>
         </is>
@@ -1944,7 +2014,7 @@
           <t>Annual depreciation</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>=(Cost-ResidualValue)/UsefulLife</t>
         </is>
@@ -1966,7 +2036,7 @@
           <t>Book value</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>=Cost-AccumulatedDepreciation</t>
         </is>
